--- a/2024-09-20018D Source Data Ext. Fig. 2.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11B0FF6-C702-4005-8C50-B72487A9804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCDB01F-834C-4D44-9475-42547C75BDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   </si>
   <si>
     <t>KE1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -127,7 +127,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -157,12 +157,6 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial Regular"/>
       <family val="2"/>
     </font>
     <font>
@@ -210,7 +204,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,10 +227,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -246,6 +236,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -522,40 +513,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10" t="s">
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
@@ -596,7 +587,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -637,73 +628,73 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27"/>
     </row>
   </sheetData>
@@ -713,7 +704,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -722,35 +713,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="30">
+    <row r="1" spans="1:22" ht="30" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A2" s="5"/>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -763,26 +754,26 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="8">
-        <v>0.26724650061919097</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.30153279310477799</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0.34427275601885399</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0.376649129603564</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0.47051791374575702</v>
-      </c>
-      <c r="J3" s="8">
-        <v>0.55432963957057901</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="E3" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.47</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -795,26 +786,26 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="8">
-        <v>0.37703251119543901</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.22767683767806801</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.105904981721115</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0.51002903692031498</v>
-      </c>
-      <c r="I4" s="8">
-        <v>0.44569138802832697</v>
-      </c>
-      <c r="J4" s="8">
-        <v>0.393371483286447</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="E4" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.11</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
@@ -827,69 +818,69 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
-        <v>0.30946678567825803</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.33852500851370199</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0.394459793478173</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0.24905905416577201</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.49060847670017699</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0.75066636542961795</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="30">
+      <c r="E5" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.39</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.49</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="30" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10" t="s">
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10" t="s">
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10" t="s">
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10" t="s">
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
@@ -957,7 +948,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
@@ -1025,10 +1016,10 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21"/>
     </row>
   </sheetData>
@@ -1044,7 +1035,7 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="H9:J9"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1053,35 +1044,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -1113,7 +1104,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1145,43 +1136,43 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17"/>
     </row>
   </sheetData>
@@ -1190,7 +1181,7 @@
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/2024-09-20018D Source Data Ext. Fig. 2.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 2.xlsx
@@ -1185,4 +1185,262 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A580DDD6E32D24793B52EBDA382135E" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="420b5df69e2a8ef095a347c37071042d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03670651-1d3f-4393-a695-0ad38e7dc27c" xmlns:ns3="98cfd510-5244-40a7-ac81-0d7d1b58424e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43051459d3b7bcd6c9644565fa79aaf6" ns2:_="" ns3:_="">
+    <xsd:import namespace="03670651-1d3f-4393-a695-0ad38e7dc27c"/>
+    <xsd:import namespace="98cfd510-5244-40a7-ac81-0d7d1b58424e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationSourceID" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:ArchiverLinkFileType" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="03670651-1d3f-4393-a695-0ad38e7dc27c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationSourceID" ma:index="8" nillable="true" ma:displayName="MigrationSourceID" ma:internalName="MigrationSourceID" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fe026092-a6d1-42a7-a35d-9d1bdd270ae7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="03670651-1d3f-4393-a695-0ad38e7dc27c">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="98cfd510-5244-40a7-ac81-0d7d1b58424e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fb58666-e629-4e5a-b780-b8dcc15b318b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ArchiverLinkFileType" ma:index="23" nillable="true" ma:displayName="ArchiverLinkFileType" ma:hidden="true" ma:internalName="ArchiverLinkFileType">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="03670651-1d3f-4393-a695-0ad38e7dc27c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ArchiverLinkFileType xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18ECE092-D668-4B9C-BEB2-46277061185E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65768521-11F6-4AAC-9571-DF7CBEE9CF51}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5978FE6E-FD9C-4C75-940C-912E63697021}"/>
 </file>